--- a/questionnaire_templates/049_trauma_informed_care_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/049_trauma_informed_care_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_difficult'}</t>
+          <t>very_difficult</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Difficult'}</t>
+          <t>Very Difficult</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_difficult'}</t>
+          <t>somewhat_difficult</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Difficult'}</t>
+          <t>Somewhat Difficult</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_easy'}</t>
+          <t>somewhat_easy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Easy'}</t>
+          <t>Somewhat Easy</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_easy'}</t>
+          <t>very_easy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Easy'}</t>
+          <t>Very Easy</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat_Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Very_Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
